--- a/results_(stress_test)_PLIxSigmoid-PLI-/cnn_evaluation(stress_test)_k-heaviside_p-30_nm_basis-False_nm_modifier-False.xlsx
+++ b/results_(stress_test)_PLIxSigmoid-PLI-/cnn_evaluation(stress_test)_k-heaviside_p-30_nm_basis-False_nm_modifier-False.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1055,6 +1055,614 @@
       </c>
       <c r="E33" t="n">
         <v>3.060067461837304</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>sub6ex1</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>85.57522123893804</v>
+      </c>
+      <c r="C34" t="n">
+        <v>84.6977086000165</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.3349343476758804</v>
+      </c>
+      <c r="E34" t="n">
+        <v>85.57522123893806</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>sub6ex2</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>89.67551622418878</v>
+      </c>
+      <c r="C35" t="n">
+        <v>88.9113321527748</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.4066427929351145</v>
+      </c>
+      <c r="E35" t="n">
+        <v>89.67551622418878</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>sub6ex3</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>88.73156342182891</v>
+      </c>
+      <c r="C36" t="n">
+        <v>88.43130440304088</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.2898258766741492</v>
+      </c>
+      <c r="E36" t="n">
+        <v>88.73156342182891</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>sub7ex1</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>85.19174041297936</v>
+      </c>
+      <c r="C37" t="n">
+        <v>85.04110895879003</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.3340011752055337</v>
+      </c>
+      <c r="E37" t="n">
+        <v>85.19174041297936</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>sub7ex2</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>85.28023598820059</v>
+      </c>
+      <c r="C38" t="n">
+        <v>85.18690837000366</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.320212822384201</v>
+      </c>
+      <c r="E38" t="n">
+        <v>85.28023598820059</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>sub7ex3</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>87.72861356932154</v>
+      </c>
+      <c r="C39" t="n">
+        <v>87.30917693527535</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.2933533031939685</v>
+      </c>
+      <c r="E39" t="n">
+        <v>87.72861356932154</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>sub8ex1</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>92.12389380530973</v>
+      </c>
+      <c r="C40" t="n">
+        <v>91.72461229982598</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.1969963341776747</v>
+      </c>
+      <c r="E40" t="n">
+        <v>92.12389380530973</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>sub8ex2</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>90.97345132743362</v>
+      </c>
+      <c r="C41" t="n">
+        <v>91.00099014104509</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.198561726056505</v>
+      </c>
+      <c r="E41" t="n">
+        <v>90.97345132743362</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>sub8ex3</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>92.21238938053098</v>
+      </c>
+      <c r="C42" t="n">
+        <v>92.15418942905515</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0.1870450291899033</v>
+      </c>
+      <c r="E42" t="n">
+        <v>92.21238938053098</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>sub9ex1</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>92.24188790560473</v>
+      </c>
+      <c r="C43" t="n">
+        <v>92.29022105177735</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0.1834491131841787</v>
+      </c>
+      <c r="E43" t="n">
+        <v>92.24188790560473</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>sub9ex2</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>91.47492625368731</v>
+      </c>
+      <c r="C44" t="n">
+        <v>91.00058444863281</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0.2191149460501038</v>
+      </c>
+      <c r="E44" t="n">
+        <v>91.47492625368731</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>sub9ex3</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>90.53097345132743</v>
+      </c>
+      <c r="C45" t="n">
+        <v>89.58596855409272</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0.3013951281725895</v>
+      </c>
+      <c r="E45" t="n">
+        <v>90.53097345132743</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>sub10ex1</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>83.00884955752213</v>
+      </c>
+      <c r="C46" t="n">
+        <v>82.53310247049663</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0.3628911756910383</v>
+      </c>
+      <c r="E46" t="n">
+        <v>83.00884955752213</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>sub10ex2</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>84.3952802359882</v>
+      </c>
+      <c r="C47" t="n">
+        <v>83.33705183488846</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0.380237132202213</v>
+      </c>
+      <c r="E47" t="n">
+        <v>84.3952802359882</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>sub10ex3</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>83.27433628318583</v>
+      </c>
+      <c r="C48" t="n">
+        <v>82.8593172429071</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0.35479864780015</v>
+      </c>
+      <c r="E48" t="n">
+        <v>83.27433628318583</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>sub11ex1</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>91.12094395280236</v>
+      </c>
+      <c r="C49" t="n">
+        <v>90.90043329191754</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0.2431223511657057</v>
+      </c>
+      <c r="E49" t="n">
+        <v>91.12094395280236</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>sub11ex2</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>91.20943952802359</v>
+      </c>
+      <c r="C50" t="n">
+        <v>91.05382826490225</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.2075995534226725</v>
+      </c>
+      <c r="E50" t="n">
+        <v>91.20943952802359</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>sub11ex3</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>90.8259587020649</v>
+      </c>
+      <c r="C51" t="n">
+        <v>90.94475314267076</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0.2322116298397305</v>
+      </c>
+      <c r="E51" t="n">
+        <v>90.8259587020649</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>sub12ex1</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>87.87610619469027</v>
+      </c>
+      <c r="C52" t="n">
+        <v>87.3112186994862</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0.3372685107053258</v>
+      </c>
+      <c r="E52" t="n">
+        <v>87.87610619469027</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>sub12ex2</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>84.01179941002951</v>
+      </c>
+      <c r="C53" t="n">
+        <v>83.92715280077303</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0.3428380081507688</v>
+      </c>
+      <c r="E53" t="n">
+        <v>84.01179941002951</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>sub12ex3</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>85.01474926253687</v>
+      </c>
+      <c r="C54" t="n">
+        <v>84.64888719034229</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0.3750490029497693</v>
+      </c>
+      <c r="E54" t="n">
+        <v>85.01474926253687</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>sub13ex1</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>87.05014749262537</v>
+      </c>
+      <c r="C55" t="n">
+        <v>87.04876298086533</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0.3188843013020232</v>
+      </c>
+      <c r="E55" t="n">
+        <v>87.05014749262537</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>sub13ex2</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>88.87905604719764</v>
+      </c>
+      <c r="C56" t="n">
+        <v>88.85703929382842</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0.2707670612454725</v>
+      </c>
+      <c r="E56" t="n">
+        <v>88.87905604719764</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>sub13ex3</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>87.58112094395281</v>
+      </c>
+      <c r="C57" t="n">
+        <v>87.69341322369998</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0.2902362492478763</v>
+      </c>
+      <c r="E57" t="n">
+        <v>87.58112094395281</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>sub14ex1</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>88.02359882005899</v>
+      </c>
+      <c r="C58" t="n">
+        <v>87.71083237321818</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0.2789737705121903</v>
+      </c>
+      <c r="E58" t="n">
+        <v>88.02359882005899</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>sub14ex2</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>86.01769911504425</v>
+      </c>
+      <c r="C59" t="n">
+        <v>85.20382871887286</v>
+      </c>
+      <c r="D59" t="n">
+        <v>0.333698067542476</v>
+      </c>
+      <c r="E59" t="n">
+        <v>86.01769911504425</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>sub14ex3</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>86.07669616519175</v>
+      </c>
+      <c r="C60" t="n">
+        <v>85.28061936308838</v>
+      </c>
+      <c r="D60" t="n">
+        <v>0.6993322051712312</v>
+      </c>
+      <c r="E60" t="n">
+        <v>86.07669616519175</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>sub15ex1</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>89.6165191740413</v>
+      </c>
+      <c r="C61" t="n">
+        <v>89.63871248622254</v>
+      </c>
+      <c r="D61" t="n">
+        <v>0.2601512547757011</v>
+      </c>
+      <c r="E61" t="n">
+        <v>89.6165191740413</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>sub15ex2</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>90.97345132743362</v>
+      </c>
+      <c r="C62" t="n">
+        <v>91.02354106035077</v>
+      </c>
+      <c r="D62" t="n">
+        <v>0.2080512590308596</v>
+      </c>
+      <c r="E62" t="n">
+        <v>90.97345132743362</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>sub15ex3</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>93.65781710914455</v>
+      </c>
+      <c r="C63" t="n">
+        <v>93.35523169115731</v>
+      </c>
+      <c r="D63" t="n">
+        <v>0.1791486021160381</v>
+      </c>
+      <c r="E63" t="n">
+        <v>93.65781710914455</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>88.34513274336285</v>
+      </c>
+      <c r="C64" t="n">
+        <v>88.02206104913397</v>
+      </c>
+      <c r="D64" t="n">
+        <v>0.2980263792590349</v>
+      </c>
+      <c r="E64" t="n">
+        <v>88.34513274336285</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Std</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>2.983926605181269</v>
+      </c>
+      <c r="C65" t="n">
+        <v>3.105956434229599</v>
+      </c>
+      <c r="D65" t="n">
+        <v>0.09892657368326241</v>
+      </c>
+      <c r="E65" t="n">
+        <v>2.983926605181269</v>
       </c>
     </row>
   </sheetData>
@@ -1068,7 +1676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1283,6 +1891,196 @@
         <v>1.603998028919112</v>
       </c>
       <c r="E11" t="inlineStr">
+        <is>
+          <t>Std</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>88.34513274336285</v>
+      </c>
+      <c r="B12" t="n">
+        <v>88.02206104913397</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.2980263792590349</v>
+      </c>
+      <c r="D12" t="n">
+        <v>88.34513274336285</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>2.983926605181269</v>
+      </c>
+      <c r="B13" t="n">
+        <v>3.105956434229599</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.09892657368326241</v>
+      </c>
+      <c r="D13" t="n">
+        <v>2.983926605181269</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Std</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>87.26745329400197</v>
+      </c>
+      <c r="B14" t="n">
+        <v>86.68739123230665</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.3369156537218078</v>
+      </c>
+      <c r="D14" t="n">
+        <v>87.26745329400197</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>2.399646341318539</v>
+      </c>
+      <c r="B15" t="n">
+        <v>2.606378506216009</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.07241029515861118</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2.39964634131854</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Std</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>87.1024460995914</v>
+      </c>
+      <c r="B16" t="n">
+        <v>86.8994900101313</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.3620398405261221</v>
+      </c>
+      <c r="D16" t="n">
+        <v>87.1024460995914</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>1.62526252442654</v>
+      </c>
+      <c r="B17" t="n">
+        <v>1.672205327538536</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.05923934502267177</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.62526252442654</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Std</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>75.41492285112039</v>
+      </c>
+      <c r="B18" t="n">
+        <v>75.16653414902034</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.6712437561722211</v>
+      </c>
+      <c r="D18" t="n">
+        <v>75.41492285112038</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>3.379210605986666</v>
+      </c>
+      <c r="B19" t="n">
+        <v>3.498953720418441</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.127788692919125</v>
+      </c>
+      <c r="D19" t="n">
+        <v>3.379210605986667</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Std</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>50.40906351554369</v>
+      </c>
+      <c r="B20" t="n">
+        <v>49.4176175393985</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1.089145991520749</v>
+      </c>
+      <c r="D20" t="n">
+        <v>50.40906351554369</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>1.373811637913355</v>
+      </c>
+      <c r="B21" t="n">
+        <v>1.508675688405925</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.033398896762361</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.373811637913354</v>
+      </c>
+      <c r="E21" t="inlineStr">
         <is>
           <t>Std</t>
         </is>
@@ -1299,7 +2097,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1472,6 +2270,136 @@
       </c>
       <c r="H6" t="n">
         <v>0.04188451928928684</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>88.34513274336285</v>
+      </c>
+      <c r="B7" t="n">
+        <v>2.983926605181269</v>
+      </c>
+      <c r="C7" t="n">
+        <v>88.02206104913397</v>
+      </c>
+      <c r="D7" t="n">
+        <v>3.105956434229599</v>
+      </c>
+      <c r="E7" t="n">
+        <v>88.34513274336285</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2.983926605181269</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.2980263792590349</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.09892657368326241</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>87.26745329400197</v>
+      </c>
+      <c r="B8" t="n">
+        <v>2.399646341318539</v>
+      </c>
+      <c r="C8" t="n">
+        <v>86.68739123230665</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.606378506216009</v>
+      </c>
+      <c r="E8" t="n">
+        <v>87.26745329400197</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2.39964634131854</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.3369156537218078</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.07241029515861118</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>87.1024460995914</v>
+      </c>
+      <c r="B9" t="n">
+        <v>1.62526252442654</v>
+      </c>
+      <c r="C9" t="n">
+        <v>86.8994900101313</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.672205327538536</v>
+      </c>
+      <c r="E9" t="n">
+        <v>87.1024460995914</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.62526252442654</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.3620398405261221</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.05923934502267177</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>75.41492285112039</v>
+      </c>
+      <c r="B10" t="n">
+        <v>3.379210605986666</v>
+      </c>
+      <c r="C10" t="n">
+        <v>75.16653414902034</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3.498953720418441</v>
+      </c>
+      <c r="E10" t="n">
+        <v>75.41492285112038</v>
+      </c>
+      <c r="F10" t="n">
+        <v>3.379210605986667</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.6712437561722211</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.127788692919125</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>50.40906351554369</v>
+      </c>
+      <c r="B11" t="n">
+        <v>1.373811637913355</v>
+      </c>
+      <c r="C11" t="n">
+        <v>49.4176175393985</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.508675688405925</v>
+      </c>
+      <c r="E11" t="n">
+        <v>50.40906351554369</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.373811637913354</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.089145991520749</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.033398896762361</v>
       </c>
     </row>
   </sheetData>
@@ -1485,7 +2413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2121,6 +3049,614 @@
       </c>
       <c r="E33" t="n">
         <v>2.061685943060722</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>sub6ex1</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>84.04129793510324</v>
+      </c>
+      <c r="C34" t="n">
+        <v>83.7540945300637</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.3751018130404797</v>
+      </c>
+      <c r="E34" t="n">
+        <v>84.04129793510324</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>sub6ex2</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>84.71976401179941</v>
+      </c>
+      <c r="C35" t="n">
+        <v>84.69058390961227</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.358440804698815</v>
+      </c>
+      <c r="E35" t="n">
+        <v>84.71976401179941</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>sub6ex3</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>87.55162241887906</v>
+      </c>
+      <c r="C36" t="n">
+        <v>87.11879667197334</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.3151609316487641</v>
+      </c>
+      <c r="E36" t="n">
+        <v>87.55162241887906</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>sub7ex1</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>84.42477876106194</v>
+      </c>
+      <c r="C37" t="n">
+        <v>83.2779256261522</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.3774339623070166</v>
+      </c>
+      <c r="E37" t="n">
+        <v>84.42477876106194</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>sub7ex2</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>86.57817109144543</v>
+      </c>
+      <c r="C38" t="n">
+        <v>85.42387092784483</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.3973775700879438</v>
+      </c>
+      <c r="E38" t="n">
+        <v>86.57817109144543</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>sub7ex3</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>85.92920353982301</v>
+      </c>
+      <c r="C39" t="n">
+        <v>85.35096170778226</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.3551960972331775</v>
+      </c>
+      <c r="E39" t="n">
+        <v>85.92920353982301</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>sub8ex1</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>91.53392330383481</v>
+      </c>
+      <c r="C40" t="n">
+        <v>91.51463413836056</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.1989421131986698</v>
+      </c>
+      <c r="E40" t="n">
+        <v>91.53392330383481</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>sub8ex2</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>90.61946902654867</v>
+      </c>
+      <c r="C41" t="n">
+        <v>90.08016293924143</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.2359472836377487</v>
+      </c>
+      <c r="E41" t="n">
+        <v>90.61946902654867</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>sub8ex3</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>92.41887905604719</v>
+      </c>
+      <c r="C42" t="n">
+        <v>92.33997820524957</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0.2058252759544606</v>
+      </c>
+      <c r="E42" t="n">
+        <v>92.41887905604719</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>sub9ex1</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>88.76106194690266</v>
+      </c>
+      <c r="C43" t="n">
+        <v>88.23037669427404</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0.3282799939780186</v>
+      </c>
+      <c r="E43" t="n">
+        <v>88.76106194690266</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>sub9ex2</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>86.07669616519175</v>
+      </c>
+      <c r="C44" t="n">
+        <v>85.9406699337939</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0.3453617932818209</v>
+      </c>
+      <c r="E44" t="n">
+        <v>86.07669616519175</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>sub9ex3</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>90.08849557522123</v>
+      </c>
+      <c r="C45" t="n">
+        <v>89.79760583303366</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0.2754243547193861</v>
+      </c>
+      <c r="E45" t="n">
+        <v>90.08849557522123</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>sub10ex1</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>84.10029498525074</v>
+      </c>
+      <c r="C46" t="n">
+        <v>82.49039768205068</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0.4576348923224335</v>
+      </c>
+      <c r="E46" t="n">
+        <v>84.10029498525074</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>sub10ex2</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>85.54572271386431</v>
+      </c>
+      <c r="C47" t="n">
+        <v>83.25394652111021</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0.4459824962531759</v>
+      </c>
+      <c r="E47" t="n">
+        <v>85.54572271386431</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>sub10ex3</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>84.98525073746313</v>
+      </c>
+      <c r="C48" t="n">
+        <v>84.41501673633348</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0.3496293016495959</v>
+      </c>
+      <c r="E48" t="n">
+        <v>84.98525073746313</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>sub11ex1</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>90.3834808259587</v>
+      </c>
+      <c r="C49" t="n">
+        <v>89.44797725655494</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0.2607112462535345</v>
+      </c>
+      <c r="E49" t="n">
+        <v>90.3834808259587</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>sub11ex2</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>91.20943952802359</v>
+      </c>
+      <c r="C50" t="n">
+        <v>91.34964989907861</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.2119269334332785</v>
+      </c>
+      <c r="E50" t="n">
+        <v>91.20943952802359</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>sub11ex3</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>88.70206489675516</v>
+      </c>
+      <c r="C51" t="n">
+        <v>87.86295240261083</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0.3200556256657971</v>
+      </c>
+      <c r="E51" t="n">
+        <v>88.70206489675516</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>sub12ex1</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>86.69616519174042</v>
+      </c>
+      <c r="C52" t="n">
+        <v>86.6947366317352</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0.3128540289918116</v>
+      </c>
+      <c r="E52" t="n">
+        <v>86.69616519174041</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>sub12ex2</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>84.57227138643069</v>
+      </c>
+      <c r="C53" t="n">
+        <v>84.51069666473242</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0.3736242297241309</v>
+      </c>
+      <c r="E53" t="n">
+        <v>84.57227138643069</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>sub12ex3</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>85.57522123893806</v>
+      </c>
+      <c r="C54" t="n">
+        <v>85.59233808688523</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0.3453397995171448</v>
+      </c>
+      <c r="E54" t="n">
+        <v>85.57522123893804</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>sub13ex1</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>86.19469026548673</v>
+      </c>
+      <c r="C55" t="n">
+        <v>85.13475192717345</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0.3836682250121763</v>
+      </c>
+      <c r="E55" t="n">
+        <v>86.19469026548673</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>sub13ex2</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>88.20058997050147</v>
+      </c>
+      <c r="C56" t="n">
+        <v>87.4243436017661</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0.3520792034105398</v>
+      </c>
+      <c r="E56" t="n">
+        <v>88.20058997050147</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>sub13ex3</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>87.75811209439527</v>
+      </c>
+      <c r="C57" t="n">
+        <v>87.46952626690715</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0.3106823432259261</v>
+      </c>
+      <c r="E57" t="n">
+        <v>87.75811209439527</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>sub14ex1</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>85.07374631268436</v>
+      </c>
+      <c r="C58" t="n">
+        <v>84.76546575450995</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0.3457304753586262</v>
+      </c>
+      <c r="E58" t="n">
+        <v>85.07374631268436</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>sub14ex2</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>85.69321533923303</v>
+      </c>
+      <c r="C59" t="n">
+        <v>85.68713036202088</v>
+      </c>
+      <c r="D59" t="n">
+        <v>0.3442399914977917</v>
+      </c>
+      <c r="E59" t="n">
+        <v>85.69321533923303</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>sub14ex3</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>88.34808259587021</v>
+      </c>
+      <c r="C60" t="n">
+        <v>87.29134555305214</v>
+      </c>
+      <c r="D60" t="n">
+        <v>0.5357648336076333</v>
+      </c>
+      <c r="E60" t="n">
+        <v>88.34808259587021</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>sub15ex1</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>87.16814159292036</v>
+      </c>
+      <c r="C61" t="n">
+        <v>86.91770523928912</v>
+      </c>
+      <c r="D61" t="n">
+        <v>0.3081603549188003</v>
+      </c>
+      <c r="E61" t="n">
+        <v>87.16814159292036</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>sub15ex2</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>85.19174041297936</v>
+      </c>
+      <c r="C62" t="n">
+        <v>83.52084351833618</v>
+      </c>
+      <c r="D62" t="n">
+        <v>0.3902398079381479</v>
+      </c>
+      <c r="E62" t="n">
+        <v>85.19174041297934</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>sub15ex3</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>89.88200589970502</v>
+      </c>
+      <c r="C63" t="n">
+        <v>89.27325174767078</v>
+      </c>
+      <c r="D63" t="n">
+        <v>0.2906538290873869</v>
+      </c>
+      <c r="E63" t="n">
+        <v>89.88200589970502</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>87.26745329400197</v>
+      </c>
+      <c r="C64" t="n">
+        <v>86.68739123230665</v>
+      </c>
+      <c r="D64" t="n">
+        <v>0.3369156537218078</v>
+      </c>
+      <c r="E64" t="n">
+        <v>87.26745329400197</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Std</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>2.399646341318539</v>
+      </c>
+      <c r="C65" t="n">
+        <v>2.606378506216009</v>
+      </c>
+      <c r="D65" t="n">
+        <v>0.07241029515861118</v>
+      </c>
+      <c r="E65" t="n">
+        <v>2.39964634131854</v>
       </c>
     </row>
   </sheetData>
@@ -2134,7 +3670,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2770,6 +4306,614 @@
       </c>
       <c r="E33" t="n">
         <v>1.706356171975203</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>sub6ex1</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>86.4306784660767</v>
+      </c>
+      <c r="C34" t="n">
+        <v>86.424656327509</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.3651123508277427</v>
+      </c>
+      <c r="E34" t="n">
+        <v>86.4306784660767</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>sub6ex2</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>86.43067846607669</v>
+      </c>
+      <c r="C35" t="n">
+        <v>86.42726362386455</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.3711415776051581</v>
+      </c>
+      <c r="E35" t="n">
+        <v>86.43067846607669</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>sub6ex3</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>87.16814159292036</v>
+      </c>
+      <c r="C36" t="n">
+        <v>86.80296477437255</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.3564397287952791</v>
+      </c>
+      <c r="E36" t="n">
+        <v>87.16814159292035</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>sub7ex1</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>85.19174041297934</v>
+      </c>
+      <c r="C37" t="n">
+        <v>85.19645038221866</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.386612683524921</v>
+      </c>
+      <c r="E37" t="n">
+        <v>85.19174041297934</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>sub7ex2</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>85.6047197640118</v>
+      </c>
+      <c r="C38" t="n">
+        <v>85.16424369909825</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.380117459630128</v>
+      </c>
+      <c r="E38" t="n">
+        <v>85.6047197640118</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>sub7ex3</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>86.10619469026548</v>
+      </c>
+      <c r="C39" t="n">
+        <v>86.10848129219993</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.3750245841045398</v>
+      </c>
+      <c r="E39" t="n">
+        <v>86.10619469026548</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>sub8ex1</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>91.17994100294985</v>
+      </c>
+      <c r="C40" t="n">
+        <v>91.38840018176354</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.2408151941844456</v>
+      </c>
+      <c r="E40" t="n">
+        <v>91.17994100294985</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>sub8ex2</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>87.28613569321534</v>
+      </c>
+      <c r="C41" t="n">
+        <v>87.18113175166923</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.3144134364692339</v>
+      </c>
+      <c r="E41" t="n">
+        <v>87.28613569321534</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>sub8ex3</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>89.35103244837758</v>
+      </c>
+      <c r="C42" t="n">
+        <v>89.48916564161094</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0.2928450454899575</v>
+      </c>
+      <c r="E42" t="n">
+        <v>89.35103244837758</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>sub9ex1</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>88.43657817109144</v>
+      </c>
+      <c r="C43" t="n">
+        <v>88.54139314167639</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0.3068045222219856</v>
+      </c>
+      <c r="E43" t="n">
+        <v>88.43657817109144</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>sub9ex2</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>86.07669616519175</v>
+      </c>
+      <c r="C44" t="n">
+        <v>85.70891045257017</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0.3829738748871023</v>
+      </c>
+      <c r="E44" t="n">
+        <v>86.07669616519175</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>sub9ex3</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>89.2330383480826</v>
+      </c>
+      <c r="C45" t="n">
+        <v>89.32381051915917</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0.2987737092480529</v>
+      </c>
+      <c r="E45" t="n">
+        <v>89.2330383480826</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>sub10ex1</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>86.13569321533923</v>
+      </c>
+      <c r="C46" t="n">
+        <v>86.1383309680424</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0.379383273391674</v>
+      </c>
+      <c r="E46" t="n">
+        <v>86.13569321533923</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>sub10ex2</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>85.78171091445428</v>
+      </c>
+      <c r="C47" t="n">
+        <v>85.49238661938156</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0.3776257856419155</v>
+      </c>
+      <c r="E47" t="n">
+        <v>85.78171091445428</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>sub10ex3</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>85.69321533923303</v>
+      </c>
+      <c r="C48" t="n">
+        <v>84.61450773922763</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0.4642351096360168</v>
+      </c>
+      <c r="E48" t="n">
+        <v>85.69321533923303</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>sub11ex1</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>90.26548672566372</v>
+      </c>
+      <c r="C49" t="n">
+        <v>89.73091997464451</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0.2788604858777641</v>
+      </c>
+      <c r="E49" t="n">
+        <v>90.26548672566372</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>sub11ex2</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>89.85804375470376</v>
+      </c>
+      <c r="C50" t="n">
+        <v>89.72290149314539</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.2661866022186586</v>
+      </c>
+      <c r="E50" t="n">
+        <v>89.85804375470376</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>sub11ex3</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>87.25663716814159</v>
+      </c>
+      <c r="C51" t="n">
+        <v>87.17976836161924</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0.3310278379009105</v>
+      </c>
+      <c r="E51" t="n">
+        <v>87.25663716814159</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>sub12ex1</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>87.02064896755162</v>
+      </c>
+      <c r="C52" t="n">
+        <v>86.96264314533914</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0.3456580649202806</v>
+      </c>
+      <c r="E52" t="n">
+        <v>87.02064896755162</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>sub12ex2</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>85.63421828908555</v>
+      </c>
+      <c r="C53" t="n">
+        <v>85.6441404436859</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0.3885209078667685</v>
+      </c>
+      <c r="E53" t="n">
+        <v>85.63421828908555</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>sub12ex3</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>84.04129793510324</v>
+      </c>
+      <c r="C54" t="n">
+        <v>84.0010125308435</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0.4573349917326898</v>
+      </c>
+      <c r="E54" t="n">
+        <v>84.04129793510324</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>sub13ex1</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>85.25073746312685</v>
+      </c>
+      <c r="C55" t="n">
+        <v>85.05821635531238</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0.3939807732453725</v>
+      </c>
+      <c r="E55" t="n">
+        <v>85.25073746312685</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>sub13ex2</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>86.8731563421829</v>
+      </c>
+      <c r="C56" t="n">
+        <v>86.54705273499711</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0.3750654623591496</v>
+      </c>
+      <c r="E56" t="n">
+        <v>86.8731563421829</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>sub13ex3</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>86.93215339233038</v>
+      </c>
+      <c r="C57" t="n">
+        <v>86.57039333358833</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0.3845066189261464</v>
+      </c>
+      <c r="E57" t="n">
+        <v>86.93215339233038</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>sub14ex1</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>86.19469026548673</v>
+      </c>
+      <c r="C58" t="n">
+        <v>85.98380567826138</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0.3984545413239782</v>
+      </c>
+      <c r="E58" t="n">
+        <v>86.19469026548673</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>sub14ex2</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>86.10619469026548</v>
+      </c>
+      <c r="C59" t="n">
+        <v>86.07499556555544</v>
+      </c>
+      <c r="D59" t="n">
+        <v>0.3761532926233485</v>
+      </c>
+      <c r="E59" t="n">
+        <v>86.10619469026548</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>sub14ex3</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>88.64306784660766</v>
+      </c>
+      <c r="C60" t="n">
+        <v>87.30381085151554</v>
+      </c>
+      <c r="D60" t="n">
+        <v>0.5418072547947911</v>
+      </c>
+      <c r="E60" t="n">
+        <v>88.64306784660766</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>sub15ex1</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>87.69911504424779</v>
+      </c>
+      <c r="C61" t="n">
+        <v>87.39112713600258</v>
+      </c>
+      <c r="D61" t="n">
+        <v>0.3437058565061307</v>
+      </c>
+      <c r="E61" t="n">
+        <v>87.69911504424779</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>sub15ex2</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>87.58112094395281</v>
+      </c>
+      <c r="C62" t="n">
+        <v>87.60417425404293</v>
+      </c>
+      <c r="D62" t="n">
+        <v>0.3529938825949405</v>
+      </c>
+      <c r="E62" t="n">
+        <v>87.58112094395281</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>sub15ex3</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>87.61061946902655</v>
+      </c>
+      <c r="C63" t="n">
+        <v>87.20764133102176</v>
+      </c>
+      <c r="D63" t="n">
+        <v>0.3346203072345816</v>
+      </c>
+      <c r="E63" t="n">
+        <v>87.61061946902655</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>87.1024460995914</v>
+      </c>
+      <c r="C64" t="n">
+        <v>86.8994900101313</v>
+      </c>
+      <c r="D64" t="n">
+        <v>0.3620398405261221</v>
+      </c>
+      <c r="E64" t="n">
+        <v>87.1024460995914</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Std</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>1.62526252442654</v>
+      </c>
+      <c r="C65" t="n">
+        <v>1.672205327538536</v>
+      </c>
+      <c r="D65" t="n">
+        <v>0.05923934502267177</v>
+      </c>
+      <c r="E65" t="n">
+        <v>1.62526252442654</v>
       </c>
     </row>
   </sheetData>
@@ -2783,7 +4927,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3419,6 +5563,614 @@
       </c>
       <c r="E33" t="n">
         <v>2.770096210777787</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>sub6ex1</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>78.87905604719764</v>
+      </c>
+      <c r="C34" t="n">
+        <v>78.2225895053936</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.5515799430354187</v>
+      </c>
+      <c r="E34" t="n">
+        <v>78.87905604719764</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>sub6ex2</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>77.55162241887906</v>
+      </c>
+      <c r="C35" t="n">
+        <v>77.16339634437909</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0.624442612034424</v>
+      </c>
+      <c r="E35" t="n">
+        <v>77.55162241887905</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>sub6ex3</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>77.85577729911158</v>
+      </c>
+      <c r="C36" t="n">
+        <v>77.77855574274375</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0.6088618132596214</v>
+      </c>
+      <c r="E36" t="n">
+        <v>77.85577729911158</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>sub7ex1</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>77.28648171696986</v>
+      </c>
+      <c r="C37" t="n">
+        <v>77.30318603700849</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0.5678501771762967</v>
+      </c>
+      <c r="E37" t="n">
+        <v>77.28648171696986</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>sub7ex2</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>76.66770473793026</v>
+      </c>
+      <c r="C38" t="n">
+        <v>76.02966640468384</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0.6280759255867452</v>
+      </c>
+      <c r="E38" t="n">
+        <v>76.66770473793025</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>sub7ex3</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>69.63563698647911</v>
+      </c>
+      <c r="C39" t="n">
+        <v>68.96686325494672</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0.8475020879258712</v>
+      </c>
+      <c r="E39" t="n">
+        <v>69.63563698647911</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>sub8ex1</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>71.11852178652065</v>
+      </c>
+      <c r="C40" t="n">
+        <v>69.9512460305436</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1.057346376000593</v>
+      </c>
+      <c r="E40" t="n">
+        <v>71.11852178652063</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>sub8ex2</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>73.45253851676918</v>
+      </c>
+      <c r="C41" t="n">
+        <v>72.51812750727075</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.8517392233634988</v>
+      </c>
+      <c r="E41" t="n">
+        <v>73.45253851676917</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>sub8ex3</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>78.53337831642142</v>
+      </c>
+      <c r="C42" t="n">
+        <v>78.4128539594081</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0.5535338653251529</v>
+      </c>
+      <c r="E42" t="n">
+        <v>78.53337831642142</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>sub9ex1</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>77.05014749262537</v>
+      </c>
+      <c r="C43" t="n">
+        <v>77.05792800265712</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0.6285464406944812</v>
+      </c>
+      <c r="E43" t="n">
+        <v>77.05014749262537</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>sub9ex2</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>77.1976401179941</v>
+      </c>
+      <c r="C44" t="n">
+        <v>77.15597809032288</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0.5943711660802364</v>
+      </c>
+      <c r="E44" t="n">
+        <v>77.1976401179941</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>sub9ex3</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>78.61356932153392</v>
+      </c>
+      <c r="C45" t="n">
+        <v>78.61772482637699</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0.5473299919782828</v>
+      </c>
+      <c r="E45" t="n">
+        <v>78.61356932153392</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>sub10ex1</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>77.1709097829566</v>
+      </c>
+      <c r="C46" t="n">
+        <v>76.82348077606932</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0.6362650380780299</v>
+      </c>
+      <c r="E46" t="n">
+        <v>77.1709097829566</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>sub10ex2</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>75.63767852663085</v>
+      </c>
+      <c r="C47" t="n">
+        <v>75.55044118456371</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0.6143806918834647</v>
+      </c>
+      <c r="E47" t="n">
+        <v>75.63767852663085</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>sub10ex3</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>68.28657687350237</v>
+      </c>
+      <c r="C48" t="n">
+        <v>68.30201556091478</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0.8477891948074102</v>
+      </c>
+      <c r="E48" t="n">
+        <v>68.28657687350236</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>sub11ex1</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>76.06242268531734</v>
+      </c>
+      <c r="C49" t="n">
+        <v>75.92744172861751</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0.6132680857554078</v>
+      </c>
+      <c r="E49" t="n">
+        <v>76.06242268531734</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>sub11ex2</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>73.45106791581243</v>
+      </c>
+      <c r="C50" t="n">
+        <v>73.29062026262402</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.6920480471725265</v>
+      </c>
+      <c r="E50" t="n">
+        <v>73.45106791581242</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>sub11ex3</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>78.90941963165771</v>
+      </c>
+      <c r="C51" t="n">
+        <v>78.640563556899</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0.5792502299882472</v>
+      </c>
+      <c r="E51" t="n">
+        <v>78.90941963165771</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>sub12ex1</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>78.73156342182891</v>
+      </c>
+      <c r="C52" t="n">
+        <v>78.46207078270081</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0.571031389106065</v>
+      </c>
+      <c r="E52" t="n">
+        <v>78.73156342182889</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>sub12ex2</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>69.91236948416508</v>
+      </c>
+      <c r="C53" t="n">
+        <v>69.55256393395213</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0.8697451733673611</v>
+      </c>
+      <c r="E53" t="n">
+        <v>69.91236948416508</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>sub12ex3</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>72.39699305357313</v>
+      </c>
+      <c r="C54" t="n">
+        <v>72.08275672643022</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0.7069945060958466</v>
+      </c>
+      <c r="E54" t="n">
+        <v>72.39699305357313</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>sub13ex1</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>69.92006851270339</v>
+      </c>
+      <c r="C55" t="n">
+        <v>69.42493384796374</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0.834940517321229</v>
+      </c>
+      <c r="E55" t="n">
+        <v>69.92006851270339</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>sub13ex2</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>79.08554572271387</v>
+      </c>
+      <c r="C56" t="n">
+        <v>79.11104964717856</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0.5782735911508401</v>
+      </c>
+      <c r="E56" t="n">
+        <v>79.08554572271386</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>sub13ex3</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>77.40637894791477</v>
+      </c>
+      <c r="C57" t="n">
+        <v>77.35319561807088</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0.573678369820118</v>
+      </c>
+      <c r="E57" t="n">
+        <v>77.40637894791477</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>sub14ex1</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>70.68486751615498</v>
+      </c>
+      <c r="C58" t="n">
+        <v>70.50885217027192</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0.7717451656237244</v>
+      </c>
+      <c r="E58" t="n">
+        <v>70.68486751615498</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>sub14ex2</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>75.19606570991098</v>
+      </c>
+      <c r="C59" t="n">
+        <v>75.17168842019191</v>
+      </c>
+      <c r="D59" t="n">
+        <v>0.6711539870748917</v>
+      </c>
+      <c r="E59" t="n">
+        <v>75.19606570991098</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>sub14ex3</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>77.1386430678466</v>
+      </c>
+      <c r="C60" t="n">
+        <v>77.07859329548803</v>
+      </c>
+      <c r="D60" t="n">
+        <v>0.5792174493428319</v>
+      </c>
+      <c r="E60" t="n">
+        <v>77.1386430678466</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>sub15ex1</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>71.22501059697748</v>
+      </c>
+      <c r="C61" t="n">
+        <v>71.09832494452871</v>
+      </c>
+      <c r="D61" t="n">
+        <v>0.8145873526732126</v>
+      </c>
+      <c r="E61" t="n">
+        <v>71.22501059697748</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>sub15ex2</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>78.17576276611389</v>
+      </c>
+      <c r="C62" t="n">
+        <v>78.14432801497246</v>
+      </c>
+      <c r="D62" t="n">
+        <v>0.5718203969299793</v>
+      </c>
+      <c r="E62" t="n">
+        <v>78.17576276611389</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>sub15ex3</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>79.21426655939931</v>
+      </c>
+      <c r="C63" t="n">
+        <v>79.29498829343711</v>
+      </c>
+      <c r="D63" t="n">
+        <v>0.5499438765148322</v>
+      </c>
+      <c r="E63" t="n">
+        <v>79.21426655939931</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>75.41492285112039</v>
+      </c>
+      <c r="C64" t="n">
+        <v>75.16653414902034</v>
+      </c>
+      <c r="D64" t="n">
+        <v>0.6712437561722211</v>
+      </c>
+      <c r="E64" t="n">
+        <v>75.41492285112038</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Std</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>3.379210605986666</v>
+      </c>
+      <c r="C65" t="n">
+        <v>3.498953720418441</v>
+      </c>
+      <c r="D65" t="n">
+        <v>0.127788692919125</v>
+      </c>
+      <c r="E65" t="n">
+        <v>3.379210605986667</v>
       </c>
     </row>
   </sheetData>
@@ -3432,7 +6184,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4070,6 +6822,614 @@
         <v>1.603998028919112</v>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>sub6ex1</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>50.13226758016938</v>
+      </c>
+      <c r="C34" t="n">
+        <v>49.63402928413085</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1.090472114086151</v>
+      </c>
+      <c r="E34" t="n">
+        <v>50.13226758016938</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>sub6ex2</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>49.98131471725534</v>
+      </c>
+      <c r="C35" t="n">
+        <v>48.39714283899269</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1.075909974177679</v>
+      </c>
+      <c r="E35" t="n">
+        <v>49.98131471725534</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>sub6ex3</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>50.34446664763536</v>
+      </c>
+      <c r="C36" t="n">
+        <v>48.59916467074289</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1.14370951851209</v>
+      </c>
+      <c r="E36" t="n">
+        <v>50.34446664763536</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>sub7ex1</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>51.51541103296741</v>
+      </c>
+      <c r="C37" t="n">
+        <v>51.08386551499312</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1.115204201141993</v>
+      </c>
+      <c r="E37" t="n">
+        <v>51.51541103296741</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>sub7ex2</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>50.78002404865094</v>
+      </c>
+      <c r="C38" t="n">
+        <v>50.33570597695176</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1.051966436704</v>
+      </c>
+      <c r="E38" t="n">
+        <v>50.78002404865094</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>sub7ex3</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>51.28322909367728</v>
+      </c>
+      <c r="C39" t="n">
+        <v>50.57860665010931</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1.046436300873756</v>
+      </c>
+      <c r="E39" t="n">
+        <v>51.28322909367728</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>sub8ex1</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>51.66497980086333</v>
+      </c>
+      <c r="C40" t="n">
+        <v>50.75418001513937</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1.045246012012164</v>
+      </c>
+      <c r="E40" t="n">
+        <v>51.66497980086333</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>sub8ex2</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>50.22958676113115</v>
+      </c>
+      <c r="C41" t="n">
+        <v>48.549918628163</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1.094921212395032</v>
+      </c>
+      <c r="E41" t="n">
+        <v>50.22958676113115</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>sub8ex3</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>50.04481007621173</v>
+      </c>
+      <c r="C42" t="n">
+        <v>49.38551495240737</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1.077457535266876</v>
+      </c>
+      <c r="E42" t="n">
+        <v>50.04481007621173</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>sub9ex1</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>48.15742350712377</v>
+      </c>
+      <c r="C43" t="n">
+        <v>47.88739480462405</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1.080407848954201</v>
+      </c>
+      <c r="E43" t="n">
+        <v>48.15742350712377</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>sub9ex2</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>50.39861936521942</v>
+      </c>
+      <c r="C44" t="n">
+        <v>49.9024658834058</v>
+      </c>
+      <c r="D44" t="n">
+        <v>1.095399614175161</v>
+      </c>
+      <c r="E44" t="n">
+        <v>50.39861936521942</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>sub9ex3</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>49.80882187562176</v>
+      </c>
+      <c r="C45" t="n">
+        <v>48.42889779242815</v>
+      </c>
+      <c r="D45" t="n">
+        <v>1.09410818417867</v>
+      </c>
+      <c r="E45" t="n">
+        <v>49.80882187562176</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>sub10ex1</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>49.57404475817265</v>
+      </c>
+      <c r="C46" t="n">
+        <v>49.16958440322439</v>
+      </c>
+      <c r="D46" t="n">
+        <v>1.062321724494298</v>
+      </c>
+      <c r="E46" t="n">
+        <v>49.57404475817265</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>sub10ex2</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>50.99654841304856</v>
+      </c>
+      <c r="C47" t="n">
+        <v>49.95563436351541</v>
+      </c>
+      <c r="D47" t="n">
+        <v>1.098856398463249</v>
+      </c>
+      <c r="E47" t="n">
+        <v>50.99654841304856</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>sub10ex3</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>49.87162518706909</v>
+      </c>
+      <c r="C48" t="n">
+        <v>48.48130373087908</v>
+      </c>
+      <c r="D48" t="n">
+        <v>1.113034156958262</v>
+      </c>
+      <c r="E48" t="n">
+        <v>49.87162518706909</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>sub11ex1</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>50.95615013970709</v>
+      </c>
+      <c r="C49" t="n">
+        <v>50.18010720465306</v>
+      </c>
+      <c r="D49" t="n">
+        <v>1.082828183968862</v>
+      </c>
+      <c r="E49" t="n">
+        <v>50.95615013970709</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>sub11ex2</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>51.43452798034586</v>
+      </c>
+      <c r="C50" t="n">
+        <v>50.90730869757555</v>
+      </c>
+      <c r="D50" t="n">
+        <v>1.028480689724286</v>
+      </c>
+      <c r="E50" t="n">
+        <v>51.43452798034584</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>sub11ex3</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>48.54834384380488</v>
+      </c>
+      <c r="C51" t="n">
+        <v>47.82597361068931</v>
+      </c>
+      <c r="D51" t="n">
+        <v>1.115960533420245</v>
+      </c>
+      <c r="E51" t="n">
+        <v>48.54834384380488</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>sub12ex1</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>51.60788588136576</v>
+      </c>
+      <c r="C52" t="n">
+        <v>50.14001389387033</v>
+      </c>
+      <c r="D52" t="n">
+        <v>1.060531703631083</v>
+      </c>
+      <c r="E52" t="n">
+        <v>51.60788588136576</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>sub12ex2</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>51.45641398281992</v>
+      </c>
+      <c r="C53" t="n">
+        <v>50.94567016096347</v>
+      </c>
+      <c r="D53" t="n">
+        <v>1.059663911660512</v>
+      </c>
+      <c r="E53" t="n">
+        <v>51.45641398281991</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>sub12ex3</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>51.15987162518707</v>
+      </c>
+      <c r="C54" t="n">
+        <v>50.46458543162774</v>
+      </c>
+      <c r="D54" t="n">
+        <v>1.073578031857808</v>
+      </c>
+      <c r="E54" t="n">
+        <v>51.15987162518707</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>sub13ex1</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>51.34655144075641</v>
+      </c>
+      <c r="C55" t="n">
+        <v>50.1113453854531</v>
+      </c>
+      <c r="D55" t="n">
+        <v>1.081540141503016</v>
+      </c>
+      <c r="E55" t="n">
+        <v>51.34655144075641</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>sub13ex2</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>49.90043166463378</v>
+      </c>
+      <c r="C56" t="n">
+        <v>48.55536148478508</v>
+      </c>
+      <c r="D56" t="n">
+        <v>1.102848541736603</v>
+      </c>
+      <c r="E56" t="n">
+        <v>49.90043166463378</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>sub13ex3</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>50.28270140745163</v>
+      </c>
+      <c r="C57" t="n">
+        <v>48.83108490769611</v>
+      </c>
+      <c r="D57" t="n">
+        <v>1.108141911029816</v>
+      </c>
+      <c r="E57" t="n">
+        <v>50.28270140745163</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>sub14ex1</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>50.3977543058331</v>
+      </c>
+      <c r="C58" t="n">
+        <v>49.16443523407172</v>
+      </c>
+      <c r="D58" t="n">
+        <v>1.057447338104248</v>
+      </c>
+      <c r="E58" t="n">
+        <v>50.3977543058331</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>sub14ex2</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>47.17947387088124</v>
+      </c>
+      <c r="C59" t="n">
+        <v>45.12282601922865</v>
+      </c>
+      <c r="D59" t="n">
+        <v>1.180367122590542</v>
+      </c>
+      <c r="E59" t="n">
+        <v>47.17947387088124</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>sub14ex3</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>48.12930907706814</v>
+      </c>
+      <c r="C60" t="n">
+        <v>47.2591330423676</v>
+      </c>
+      <c r="D60" t="n">
+        <v>1.13971713980039</v>
+      </c>
+      <c r="E60" t="n">
+        <v>48.12930907706814</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>sub15ex1</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>49.03978408117717</v>
+      </c>
+      <c r="C61" t="n">
+        <v>47.74840963651467</v>
+      </c>
+      <c r="D61" t="n">
+        <v>1.143420800566673</v>
+      </c>
+      <c r="E61" t="n">
+        <v>49.03978408117717</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>sub15ex2</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>51.36999455012587</v>
+      </c>
+      <c r="C62" t="n">
+        <v>50.75788638891419</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1.05832534134388</v>
+      </c>
+      <c r="E62" t="n">
+        <v>51.36999455012587</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>sub15ex3</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>54.67953875033521</v>
+      </c>
+      <c r="C63" t="n">
+        <v>53.37097557383709</v>
+      </c>
+      <c r="D63" t="n">
+        <v>1.096077122290929</v>
+      </c>
+      <c r="E63" t="n">
+        <v>54.67953875033521</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>50.40906351554369</v>
+      </c>
+      <c r="C64" t="n">
+        <v>49.4176175393985</v>
+      </c>
+      <c r="D64" t="n">
+        <v>1.089145991520749</v>
+      </c>
+      <c r="E64" t="n">
+        <v>50.40906351554369</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Std</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>1.373811637913355</v>
+      </c>
+      <c r="C65" t="n">
+        <v>1.508675688405925</v>
+      </c>
+      <c r="D65" t="n">
+        <v>0.033398896762361</v>
+      </c>
+      <c r="E65" t="n">
+        <v>1.373811637913354</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
